--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer - AWS (Snowflake)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SG360</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wheeling, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
+          <t>https://www.indeed.com/viewjob?jk=66fc8bb22a057543</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>SG360</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Wheeling, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,112 +626,112 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab8193139c1b64e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Senior Software Engineer - Pulse</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=b049918e487f3877</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior BizOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Junior Software Developer (Virtual, Full Time)</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WEALTHCOUNSEL LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data/Modeling Engineer V</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, NoSQL, Data Modeling, MLOps, MLflow, Airflow</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c47cbacfde96e81</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Junior Software Developer (Virtual, Full Time)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>WEALTHCOUNSEL LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,192 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer (Part-time Contracted)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NORTHBAY NURSING INSTITUTE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Pulse</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b049918e487f3877</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Pulse</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b049918e487f3877</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior BizOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior BizOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Software Developer (Virtual, Full Time)</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WEALTHCOUNSEL LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Junior Software Developer (Virtual, Full Time)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>WEALTHCOUNSEL LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,15 +2936,155 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Engineer (Part-time Contracted)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NORTHBAY NURSING INSTITUTE</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,112 +906,112 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>NORTHBAY NURSING INSTITUTE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Pulse</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b049918e487f3877</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Pulse</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b049918e487f3877</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior BizOps Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Senior BizOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Software Developer (Virtual, Full Time)</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WEALTHCOUNSEL LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Data Engineer/DBA (Temporary)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=965bdb94e0f24ee4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Junior Software Developer (Virtual, Full Time)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>WEALTHCOUNSEL LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,85 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,12 +923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NORTHBAY NURSING INSTITUTE</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Pulse</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b049918e487f3877</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior BizOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,129 +2281,129 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer/DBA (Temporary)</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965bdb94e0f24ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Software Developer (Virtual, Full Time)</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WEALTHCOUNSEL LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HB Mechanical Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3015,146 +3015,6 @@
         </is>
       </c>
       <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer (Part-time Contracted)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Platform Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>HB Mechanical Group</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS (Snowflake)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66fc8bb22a057543</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SG360</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wheeling, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
+          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,147 +626,147 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,15 +3006,85 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer - AWS (Snowflake)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bcfb79ed1af62a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
         </is>
       </c>
     </row>
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,49 +951,49 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,85 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Product Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,50 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,49 +951,49 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Product Software Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Product Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,50 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -958,12 +958,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Product Software Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Product Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,95 +608,95 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>NORTHBAY NURSING INSTITUTE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
@@ -2043,25 +2043,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior BizOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Product Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Product Software Engineer</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
+          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Data Engineer/DBA (Temporary)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
+          <t>https://www.indeed.com/viewjob?jk=965bdb94e0f24ee4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Junior Software Developer (Virtual, Full Time)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WEALTHCOUNSEL LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,50 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,139 +591,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NORTHBAY NURSING INSTITUTE</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior BizOps Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b341c5698ad644e</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Product Software Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer/DBA (Temporary)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965bdb94e0f24ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Software Developer (Virtual, Full Time)</t>
+          <t>Software Engineer (Part-time Contracted)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WEALTHCOUNSEL LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, DynamoDB, NoSQL, ELT, CI/CD, Git</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6e4bc2f2ae96ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,147 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer (Part-time Contracted)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Platform Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>HB Mechanical Group</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Cognos Analytics Technical Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,129 +706,129 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8543109d9b5da2c7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Cognos Analytics Technical Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=51cf57cdde81abbd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cognos Analytics Technical Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=196851018666f4cc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,46 +1007,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Machine Learning Operations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,137 +2386,137 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7259d80e187d5e6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2818,20 +2818,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,207 +2876,207 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=cc34dbed6e7d6bf5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,40 +3121,565 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Marietta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FujiFilm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AAA Central Penn</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Engineer - Healthcare (Remote)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data AI Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Intellitech llc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Colonial Pipeline Company</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f8f89669fc5e5d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OIPA Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer (Part-time Contracted)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>KPMG</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D93" t="n">
         <v>10.4</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -993,52 +993,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Full Stack Java Developer - (Senior)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Operations</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,94 +1826,94 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7259d80e187d5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc34dbed6e7d6bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,52 +3216,52 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8f89669fc5e5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3536,19 +3536,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer (Part-time Contracted)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1baa3c7f5936cb42</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Full Stack Java Developer - (Senior)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer - (Senior)</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,94 +1756,94 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,104 +2481,104 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3645,41 +3645,6 @@
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AWS (Snowflake)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VaxCare</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7612e10491ad26f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bcfb79ed1af62a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS (Snowflake)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bcfb79ed1af62a</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
         </is>
       </c>
     </row>
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Cognos Analytics Technical Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8543109d9b5da2c7</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8543109d9b5da2c7</t>
+          <t>https://www.indeed.com/viewjob?jk=51cf57cdde81abbd</t>
         </is>
       </c>
     </row>
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cf57cdde81abbd</t>
+          <t>https://www.indeed.com/viewjob?jk=196851018666f4cc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cognos Analytics Technical Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196851018666f4cc</t>
+          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer - (Senior)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,129 +1406,129 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer - (Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=28d495042e92610a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,94 +2001,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,172 +2981,172 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,260 +3391,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Data AI Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Intellitech llc</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Colonial Pipeline Company</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>OIPA Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer - (Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer - (Senior)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d495042e92610a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,139 +1606,139 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=28d495042e92610a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,29 +2236,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
         </is>
       </c>
     </row>
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,77 +2866,77 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3295,111 +3295,6 @@
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>OIPA Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>NORTHBAY NURSING INSTITUTE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer - (Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Java Developer - (Senior)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=c431c339f092680f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=2f07b81ae5350983</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer 2 (Full-Time) - Special Projects Department</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Church of Jesus Christ of Latter-day Saints</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer, Zoom Contact Center</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=92d98bc10c1b1155</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Colonial Pipeline Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Production Support Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,225 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e210ae383840f90</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Resiliency and Recovery Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer/DBA (Temporary)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>University Of Washington</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=965bdb94e0f24ee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>

--- a/results/job_matches_2026-04-03.xlsx
+++ b/results/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cognos Analytics Technical Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8543109d9b5da2c7</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cognos Analytics Technical Consultant</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cf57cdde81abbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cognos Analytics Technical Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196851018666f4cc</t>
+          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488efb485a279681</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NORTHBAY NURSING INSTITUTE</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20d74879398cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, Databricks, Hadoop, Hive, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bbd6b498aedf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer - (Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>LIBERTY Dental Plan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b734a39dfcced490</t>
+          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe68969ff58c1600</t>
+          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d495042e92610a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242aa0084fdb7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Insight IT Pty</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Operations Engineer, Baku</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,129 +1966,129 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Operations Engineer, Baku</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004242e0072b4746</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c431c339f092680f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f07b81ae5350983</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c431c339f092680f</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f07b81ae5350983</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, SQL Server, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b66f71baeacc2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Software Engineer III - ML</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
@@ -2678,20 +2678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Zoom Contact Center</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d98bc10c1b1155</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5fd7d586fc25a</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a282ccb9c20676c</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,470 +3041,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Alternate Solutions Health Network</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef3db75965d2a75</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Experian</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Data AI Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Intellitech llc</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e210ae383840f90</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Engineer/DBA (Temporary)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>University Of Washington</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=965bdb94e0f24ee4</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
         </is>
